--- a/data/La Liga.xlsx
+++ b/data/La Liga.xlsx
@@ -1,36 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30120"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F867A19A-7A5A-4253-B500-D15FE6E5CAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="10" activeTab="15"/>
   </bookViews>
   <sheets>
-    <sheet name="Jornada 23" sheetId="1" r:id="rId1"/>
-    <sheet name="Jornada 24" sheetId="2" r:id="rId2"/>
-    <sheet name="Jornada 25" sheetId="3" r:id="rId3"/>
-    <sheet name="Jornada 26" sheetId="4" r:id="rId4"/>
-    <sheet name="Jornada 27" sheetId="5" r:id="rId5"/>
-    <sheet name="Jornada 28" sheetId="6" r:id="rId6"/>
-    <sheet name="Jornada 29" sheetId="7" r:id="rId7"/>
-    <sheet name="Jornada 31" sheetId="9" r:id="rId8"/>
-    <sheet name="Jornada 32" sheetId="10" r:id="rId9"/>
-    <sheet name="Jornada 33" sheetId="11" r:id="rId10"/>
-    <sheet name="Jornada 34" sheetId="12" r:id="rId11"/>
-    <sheet name="Jornada 30" sheetId="8" r:id="rId12"/>
-    <sheet name="Jornada 35" sheetId="13" r:id="rId13"/>
-    <sheet name="Jornada 36" sheetId="14" r:id="rId14"/>
-    <sheet name="Jornada 37" sheetId="15" r:id="rId15"/>
-    <sheet name="Jornada 38" sheetId="16" r:id="rId16"/>
+    <sheet sheetId="1" name="Jornada 23" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Jornada 24" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Jornada 25" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Jornada 26" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Jornada 27" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Jornada 28" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Jornada 29" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="Jornada 31" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="Jornada 32" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="Jornada 33" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="Jornada 34" state="visible" r:id="rId14"/>
+    <sheet sheetId="8" name="Jornada 30" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Jornada 35" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Jornada 36" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Jornada 37" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Jornada 38" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="Jornada 1" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="Jornada 2" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="Jornada 3" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="Jornada 4" state="visible" r:id="rId23"/>
+    <sheet sheetId="21" name="Jornada 5" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="Jornada 6" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="Jornada 7" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Jornada 8" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="139">
   <si>
     <t>Matchday</t>
   </si>
@@ -345,19 +352,121 @@
   </si>
   <si>
     <t>24/05/2026</t>
+  </si>
+  <si>
+    <t>Jornada 1</t>
+  </si>
+  <si>
+    <t>15/08/2026</t>
+  </si>
+  <si>
+    <t>2:30 PM</t>
+  </si>
+  <si>
+    <t>16/08/2026</t>
+  </si>
+  <si>
+    <t>12:00 PM</t>
+  </si>
+  <si>
+    <t>Racing</t>
+  </si>
+  <si>
+    <t>17/08/2026</t>
+  </si>
+  <si>
+    <t>Dep. A Coruña</t>
+  </si>
+  <si>
+    <t>19/08/2026</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>25/08/2026</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>27/08/2026</t>
+  </si>
+  <si>
+    <t>Jornada 2</t>
+  </si>
+  <si>
+    <t>20/08/2026</t>
+  </si>
+  <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
+    <t>22/08/2026</t>
+  </si>
+  <si>
+    <t>23/08/2026</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>Jornada 3</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>Jornada 4</t>
+  </si>
+  <si>
+    <t>06/09/2026</t>
+  </si>
+  <si>
+    <t>Jornada 5</t>
+  </si>
+  <si>
+    <t>13/09/2026</t>
+  </si>
+  <si>
+    <t>Jornada 6</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>Jornada 7</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>Jornada 8</t>
+  </si>
+  <si>
+    <t>11/10/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -366,8 +475,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -737,9 +844,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
@@ -1005,14 +1112,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1047,22 +1154,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -1070,22 +1177,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
         <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1093,22 +1200,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
         <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -1116,22 +1223,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
         <v>72</v>
       </c>
       <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1139,22 +1246,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
         <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1162,22 +1269,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1185,22 +1292,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
         <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -1208,22 +1315,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
         <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1231,22 +1338,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
         <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -1254,22 +1361,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
         <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -1277,14 +1384,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1319,22 +1426,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
         <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -1342,22 +1449,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
         <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1365,22 +1472,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
         <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -1388,22 +1495,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
         <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1411,22 +1518,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
         <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1434,22 +1541,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1457,22 +1564,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
         <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -1480,22 +1587,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1503,22 +1610,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -1526,22 +1633,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
         <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -1549,14 +1656,1375 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1591,22 +3059,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -1614,22 +3082,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1637,22 +3105,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -1660,22 +3128,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1683,22 +3151,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1706,22 +3174,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1729,22 +3197,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -1752,22 +3220,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1775,22 +3243,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -1798,22 +3266,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -1821,14 +3289,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1863,22 +3331,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -1886,22 +3354,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1909,22 +3377,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -1932,19 +3400,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -1955,22 +3423,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1978,19 +3446,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -2001,22 +3469,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2024,22 +3492,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2047,22 +3515,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2070,22 +3538,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2093,14 +3561,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2135,22 +3603,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
         <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -2158,22 +3626,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -2181,22 +3649,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -2204,22 +3672,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
         <v>92</v>
       </c>
       <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -2227,22 +3695,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -2250,22 +3718,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2273,22 +3741,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2296,22 +3764,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2319,22 +3787,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2342,22 +3810,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2365,559 +3833,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
@@ -3183,14 +4106,1374 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
@@ -3456,14 +5739,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
@@ -3729,14 +6012,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
@@ -4002,14 +6285,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
@@ -4275,14 +6558,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -4547,14 +6830,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -4589,22 +6872,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -4612,22 +6895,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -4635,22 +6918,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -4658,22 +6941,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -4681,22 +6964,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -4704,22 +6987,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -4727,22 +7010,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -4750,22 +7033,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -4773,22 +7056,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -4796,22 +7079,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -4819,14 +7102,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -4861,22 +7144,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
         <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -4884,22 +7167,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
         <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -4907,22 +7190,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
         <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -4930,22 +7213,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
         <v>72</v>
       </c>
       <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -4953,22 +7236,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
         <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -4976,22 +7259,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -4999,22 +7282,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
         <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -5022,22 +7305,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
         <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -5045,22 +7328,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -5068,22 +7351,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
         <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -5091,6 +7374,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>